--- a/3dpack2.xlsx
+++ b/3dpack2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d6efecc3210076de/Desktop/Acad/MTP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="180" documentId="8_{264CFC6C-0552-4E79-AC5E-12A4E536DF80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{31C1D998-33D3-4DF6-A903-80F5B323B7FA}"/>
+  <xr:revisionPtr revIDLastSave="210" documentId="8_{264CFC6C-0552-4E79-AC5E-12A4E536DF80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{316B3259-B59A-47B5-A211-457E9464C3C3}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{48667665-2070-4B77-AF56-5C458F011BCB}"/>
+    <workbookView xWindow="5712" yWindow="3360" windowWidth="17280" windowHeight="8880" xr2:uid="{48667665-2070-4B77-AF56-5C458F011BCB}"/>
   </bookViews>
   <sheets>
     <sheet name="SKU" sheetId="1" r:id="rId1"/>
@@ -433,7 +433,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{006BDADF-01D5-4C94-B959-14B47C9BA51E}">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
@@ -458,16 +458,16 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -475,50 +475,16 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -528,7 +494,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECFAED6D-E511-434C-804E-F193708C4E45}">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="14.88671875" customWidth="1"/>
@@ -562,16 +528,36 @@
         <v>2</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E2">
         <v>2</v>
       </c>
       <c r="F2">
         <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="C3">
+        <v>5</v>
+      </c>
+      <c r="D3">
+        <v>6</v>
+      </c>
+      <c r="E3">
+        <v>4</v>
+      </c>
+      <c r="F3">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/3dpack2.xlsx
+++ b/3dpack2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d6efecc3210076de/Desktop/Acad/MTP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="210" documentId="8_{264CFC6C-0552-4E79-AC5E-12A4E536DF80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{316B3259-B59A-47B5-A211-457E9464C3C3}"/>
+  <xr:revisionPtr revIDLastSave="215" documentId="8_{264CFC6C-0552-4E79-AC5E-12A4E536DF80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3C991CCD-33D6-49D1-A3A3-D3A5FB6F1A4B}"/>
   <bookViews>
-    <workbookView xWindow="5712" yWindow="3360" windowWidth="17280" windowHeight="8880" xr2:uid="{48667665-2070-4B77-AF56-5C458F011BCB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{48667665-2070-4B77-AF56-5C458F011BCB}"/>
   </bookViews>
   <sheets>
     <sheet name="SKU" sheetId="1" r:id="rId1"/>
@@ -433,7 +433,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{006BDADF-01D5-4C94-B959-14B47C9BA51E}">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
@@ -468,23 +468,6 @@
       </c>
       <c r="E2">
         <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>6</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-      <c r="D3">
-        <v>5</v>
-      </c>
-      <c r="E3">
-        <v>7</v>
       </c>
     </row>
   </sheetData>
